--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260623.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
